--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291324</v>
+        <v>128291352</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496609</v>
+        <v>496573</v>
       </c>
       <c r="R20" t="n">
-        <v>6773957</v>
+        <v>6774008</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R21" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291353</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496606</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6774292</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291026</v>
+        <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496584</v>
+        <v>496633</v>
       </c>
       <c r="R16" t="n">
-        <v>6773405</v>
+        <v>6773937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291351</v>
+        <v>128291026</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496519</v>
+        <v>496584</v>
       </c>
       <c r="R17" t="n">
-        <v>6773715</v>
+        <v>6773405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291330</v>
+        <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496633</v>
+        <v>496519</v>
       </c>
       <c r="R18" t="n">
-        <v>6773937</v>
+        <v>6773715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291352</v>
+        <v>128291324</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496573</v>
+        <v>496609</v>
       </c>
       <c r="R20" t="n">
-        <v>6774008</v>
+        <v>6773957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291353</v>
+        <v>128291352</v>
       </c>
       <c r="B21" t="n">
         <v>79029</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496606</v>
+        <v>496573</v>
       </c>
       <c r="R21" t="n">
-        <v>6774292</v>
+        <v>6774008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291353</v>
       </c>
       <c r="B22" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496606</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6774292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291330</v>
+        <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496633</v>
+        <v>496584</v>
       </c>
       <c r="R16" t="n">
-        <v>6773937</v>
+        <v>6773405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291026</v>
+        <v>128291351</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496584</v>
+        <v>496519</v>
       </c>
       <c r="R17" t="n">
-        <v>6773405</v>
+        <v>6773715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291351</v>
+        <v>128291330</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496519</v>
+        <v>496633</v>
       </c>
       <c r="R18" t="n">
-        <v>6773715</v>
+        <v>6773937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128240975</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128240684</v>
       </c>
       <c r="B3" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128291335</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128291325</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128291333</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128291029</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>128291349</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128291347</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128291343</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291026</v>
+        <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496584</v>
+        <v>496633</v>
       </c>
       <c r="R16" t="n">
-        <v>6773405</v>
+        <v>6773937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291351</v>
+        <v>128291026</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496519</v>
+        <v>496584</v>
       </c>
       <c r="R17" t="n">
-        <v>6773715</v>
+        <v>6773405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291330</v>
+        <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496633</v>
+        <v>496519</v>
       </c>
       <c r="R18" t="n">
-        <v>6773937</v>
+        <v>6773715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2519,7 @@
         <v>128291021</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291324</v>
+        <v>128291352</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496609</v>
+        <v>496573</v>
       </c>
       <c r="R20" t="n">
-        <v>6773957</v>
+        <v>6774008</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R21" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291353</v>
+        <v>128291324</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496606</v>
+        <v>496609</v>
       </c>
       <c r="R22" t="n">
-        <v>6774292</v>
+        <v>6773957</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,7 +2947,7 @@
         <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>128291328</v>
       </c>
       <c r="B24" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>128291028</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128291018</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128291013</v>
+        <v>128291322</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496513</v>
+        <v>496530</v>
       </c>
       <c r="R28" t="n">
-        <v>6773005</v>
+        <v>6774395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>äldre spår på gran</t>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128291322</v>
+        <v>128291013</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496530</v>
+        <v>496513</v>
       </c>
       <c r="R29" t="n">
-        <v>6774395</v>
+        <v>6773005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>högt upp i tall</t>
+          <t>äldre spår på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>128311720</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128240975</v>
       </c>
       <c r="B2" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128240684</v>
       </c>
       <c r="B3" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128291335</v>
       </c>
       <c r="B4" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128291325</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291333</v>
+        <v>128291029</v>
       </c>
       <c r="B6" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496585</v>
+        <v>496621</v>
       </c>
       <c r="R6" t="n">
-        <v>6774537</v>
+        <v>6773167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291029</v>
+        <v>128291349</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496621</v>
+        <v>496580</v>
       </c>
       <c r="R7" t="n">
-        <v>6773167</v>
+        <v>6774075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291349</v>
+        <v>128291333</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496580</v>
+        <v>496585</v>
       </c>
       <c r="R8" t="n">
-        <v>6774075</v>
+        <v>6774537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B9" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R9" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R10" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B11" t="n">
-        <v>57670</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R11" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R12" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128291347</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128291343</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291330</v>
+        <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496633</v>
+        <v>496584</v>
       </c>
       <c r="R16" t="n">
-        <v>6773937</v>
+        <v>6773405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291026</v>
+        <v>128291351</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496584</v>
+        <v>496519</v>
       </c>
       <c r="R17" t="n">
-        <v>6773405</v>
+        <v>6773715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291351</v>
+        <v>128291330</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>57682</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496519</v>
+        <v>496633</v>
       </c>
       <c r="R18" t="n">
-        <v>6773715</v>
+        <v>6773937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2519,7 @@
         <v>128291021</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128291352</v>
       </c>
       <c r="B20" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>128291353</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57670</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,7 +3054,7 @@
         <v>128291328</v>
       </c>
       <c r="B24" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>128291028</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>128291018</v>
       </c>
       <c r="B26" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>128291322</v>
       </c>
       <c r="B28" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>128291013</v>
       </c>
       <c r="B29" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>128311720</v>
       </c>
       <c r="B31" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R11" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R12" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B22" t="n">
-        <v>57682</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128291328</v>
+        <v>128291028</v>
       </c>
       <c r="B24" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496524</v>
+        <v>496510</v>
       </c>
       <c r="R24" t="n">
-        <v>6773501</v>
+        <v>6773105</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128291028</v>
+        <v>128291328</v>
       </c>
       <c r="B25" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496510</v>
+        <v>496524</v>
       </c>
       <c r="R25" t="n">
-        <v>6773105</v>
+        <v>6773501</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128291025</v>
+        <v>128291322</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,34 +3383,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496582</v>
+        <v>496530</v>
       </c>
       <c r="R27" t="n">
-        <v>6773525</v>
+        <v>6774395</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3450,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,7 +3460,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,7 +3492,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128291322</v>
+        <v>128291013</v>
       </c>
       <c r="B28" t="n">
         <v>57685</v>
@@ -3512,7 +3525,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3522,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496530</v>
+        <v>496513</v>
       </c>
       <c r="R28" t="n">
-        <v>6774395</v>
+        <v>6773005</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3570,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3580,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>högt upp i tall</t>
+          <t>äldre spår på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,10 +3612,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128291013</v>
+        <v>128291025</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,42 +3623,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496513</v>
+        <v>496582</v>
       </c>
       <c r="R29" t="n">
-        <v>6773005</v>
+        <v>6773525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3687,12 +3692,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:17</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>äldre spår på gran</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291029</v>
+        <v>128291333</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496621</v>
+        <v>496585</v>
       </c>
       <c r="R6" t="n">
-        <v>6773167</v>
+        <v>6774537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291349</v>
+        <v>128291029</v>
       </c>
       <c r="B7" t="n">
         <v>79083</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496580</v>
+        <v>496621</v>
       </c>
       <c r="R7" t="n">
-        <v>6774075</v>
+        <v>6773167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291333</v>
+        <v>128291349</v>
       </c>
       <c r="B8" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496585</v>
+        <v>496580</v>
       </c>
       <c r="R8" t="n">
-        <v>6774537</v>
+        <v>6774075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R9" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B10" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R10" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R11" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R12" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R14" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R15" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291026</v>
+        <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496584</v>
+        <v>496633</v>
       </c>
       <c r="R16" t="n">
-        <v>6773405</v>
+        <v>6773937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291351</v>
+        <v>128291026</v>
       </c>
       <c r="B17" t="n">
         <v>79083</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496519</v>
+        <v>496584</v>
       </c>
       <c r="R17" t="n">
-        <v>6773715</v>
+        <v>6773405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291330</v>
+        <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496633</v>
+        <v>496519</v>
       </c>
       <c r="R18" t="n">
-        <v>6773937</v>
+        <v>6773715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128291322</v>
+        <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,42 +3383,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496530</v>
+        <v>496582</v>
       </c>
       <c r="R27" t="n">
-        <v>6774395</v>
+        <v>6773525</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,7 +3442,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3460,12 +3452,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>högt upp i tall</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3612,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128291025</v>
+        <v>128291322</v>
       </c>
       <c r="B29" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3623,34 +3610,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496582</v>
+        <v>496530</v>
       </c>
       <c r="R29" t="n">
-        <v>6773525</v>
+        <v>6774395</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3692,7 +3687,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57682</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R11" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R12" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B14" t="n">
         <v>79083</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R14" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B15" t="n">
         <v>79083</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R15" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>57685</v>
+        <v>57682</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57682</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128240975</v>
       </c>
       <c r="B2" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128240684</v>
       </c>
       <c r="B3" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128291335</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128291325</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128291333</v>
       </c>
       <c r="B6" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128291029</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>128291349</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128291347</v>
       </c>
       <c r="B14" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128291343</v>
       </c>
       <c r="B15" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128291026</v>
       </c>
       <c r="B17" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>128291021</v>
       </c>
       <c r="B19" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291352</v>
+        <v>128291324</v>
       </c>
       <c r="B20" t="n">
-        <v>79083</v>
+        <v>57689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496573</v>
+        <v>496609</v>
       </c>
       <c r="R20" t="n">
-        <v>6774008</v>
+        <v>6773957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291353</v>
+        <v>128291352</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496606</v>
+        <v>496573</v>
       </c>
       <c r="R21" t="n">
-        <v>6774292</v>
+        <v>6774008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291353</v>
       </c>
       <c r="B22" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496606</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6774292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128291028</v>
+        <v>128291328</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496510</v>
+        <v>496524</v>
       </c>
       <c r="R24" t="n">
-        <v>6773105</v>
+        <v>6773501</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128291328</v>
+        <v>128291028</v>
       </c>
       <c r="B25" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496524</v>
+        <v>496510</v>
       </c>
       <c r="R25" t="n">
-        <v>6773501</v>
+        <v>6773105</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,7 +3268,7 @@
         <v>128291018</v>
       </c>
       <c r="B26" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3479,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128291013</v>
+        <v>128291322</v>
       </c>
       <c r="B28" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3522,10 +3522,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496513</v>
+        <v>496530</v>
       </c>
       <c r="R28" t="n">
-        <v>6773005</v>
+        <v>6774395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>äldre spår på gran</t>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3599,10 +3599,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128291322</v>
+        <v>128291013</v>
       </c>
       <c r="B29" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496530</v>
+        <v>496513</v>
       </c>
       <c r="R29" t="n">
-        <v>6774395</v>
+        <v>6773005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>högt upp i tall</t>
+          <t>äldre spår på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>128311720</v>
       </c>
       <c r="B31" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R9" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R10" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291330</v>
+        <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496633</v>
+        <v>496584</v>
       </c>
       <c r="R16" t="n">
-        <v>6773937</v>
+        <v>6773405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291026</v>
+        <v>128291351</v>
       </c>
       <c r="B17" t="n">
         <v>79087</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496584</v>
+        <v>496519</v>
       </c>
       <c r="R17" t="n">
-        <v>6773405</v>
+        <v>6773715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291351</v>
+        <v>128291330</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496519</v>
+        <v>496633</v>
       </c>
       <c r="R18" t="n">
-        <v>6773715</v>
+        <v>6773937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291324</v>
+        <v>128291352</v>
       </c>
       <c r="B20" t="n">
-        <v>57689</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496609</v>
+        <v>496573</v>
       </c>
       <c r="R20" t="n">
-        <v>6773957</v>
+        <v>6774008</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B21" t="n">
         <v>79087</v>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R21" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291353</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496606</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6774292</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291333</v>
+        <v>128291349</v>
       </c>
       <c r="B6" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496585</v>
+        <v>496580</v>
       </c>
       <c r="R6" t="n">
-        <v>6774537</v>
+        <v>6774075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
         <v>128291029</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291349</v>
+        <v>128291333</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496580</v>
+        <v>496585</v>
       </c>
       <c r="R8" t="n">
-        <v>6774075</v>
+        <v>6774537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R9" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R10" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R11" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R12" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R14" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R15" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
         <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128291351</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R20" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291353</v>
+        <v>128291352</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496606</v>
+        <v>496573</v>
       </c>
       <c r="R21" t="n">
-        <v>6774292</v>
+        <v>6774008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128291328</v>
+        <v>128291028</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496524</v>
+        <v>496510</v>
       </c>
       <c r="R24" t="n">
-        <v>6773501</v>
+        <v>6773105</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128291028</v>
+        <v>128291328</v>
       </c>
       <c r="B25" t="n">
-        <v>79087</v>
+        <v>57686</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496510</v>
+        <v>496524</v>
       </c>
       <c r="R25" t="n">
-        <v>6773105</v>
+        <v>6773501</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3375,7 +3375,7 @@
         <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57686</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R11" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R12" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>57689</v>
+        <v>57686</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57689</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291026</v>
+        <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496584</v>
+        <v>496633</v>
       </c>
       <c r="R16" t="n">
-        <v>6773405</v>
+        <v>6773937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291351</v>
+        <v>128291026</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496519</v>
+        <v>496584</v>
       </c>
       <c r="R17" t="n">
-        <v>6773715</v>
+        <v>6773405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291330</v>
+        <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496633</v>
+        <v>496519</v>
       </c>
       <c r="R18" t="n">
-        <v>6773937</v>
+        <v>6773715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291349</v>
+        <v>128291029</v>
       </c>
       <c r="B6" t="n">
         <v>79089</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496580</v>
+        <v>496621</v>
       </c>
       <c r="R6" t="n">
-        <v>6774075</v>
+        <v>6773167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291029</v>
+        <v>128291349</v>
       </c>
       <c r="B7" t="n">
         <v>79089</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496621</v>
+        <v>496580</v>
       </c>
       <c r="R7" t="n">
-        <v>6773167</v>
+        <v>6774075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B14" t="n">
         <v>79089</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R14" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B15" t="n">
         <v>79089</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R15" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291330</v>
+        <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496633</v>
+        <v>496584</v>
       </c>
       <c r="R16" t="n">
-        <v>6773937</v>
+        <v>6773405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291026</v>
+        <v>128291351</v>
       </c>
       <c r="B17" t="n">
         <v>79089</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496584</v>
+        <v>496519</v>
       </c>
       <c r="R17" t="n">
-        <v>6773405</v>
+        <v>6773715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291351</v>
+        <v>128291330</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496519</v>
+        <v>496633</v>
       </c>
       <c r="R18" t="n">
-        <v>6773715</v>
+        <v>6773937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291353</v>
+        <v>128291331</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496606</v>
+        <v>496594</v>
       </c>
       <c r="R20" t="n">
-        <v>6774292</v>
+        <v>6774151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291352</v>
+        <v>128291324</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496573</v>
+        <v>496609</v>
       </c>
       <c r="R21" t="n">
-        <v>6774008</v>
+        <v>6773957</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291352</v>
       </c>
       <c r="B22" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496573</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6774008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291353</v>
       </c>
       <c r="B23" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496606</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128291028</v>
+        <v>128291328</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496510</v>
+        <v>496524</v>
       </c>
       <c r="R24" t="n">
-        <v>6773105</v>
+        <v>6773501</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128291328</v>
+        <v>128291028</v>
       </c>
       <c r="B25" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496524</v>
+        <v>496510</v>
       </c>
       <c r="R25" t="n">
-        <v>6773501</v>
+        <v>6773105</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128240975</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>128240684</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128291335</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>128291325</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>128291029</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128291349</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
         <v>128291333</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B11" t="n">
-        <v>57686</v>
+        <v>8450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R11" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B12" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R12" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>128291347</v>
       </c>
       <c r="B14" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>128291343</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291026</v>
+        <v>128291330</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496584</v>
+        <v>496633</v>
       </c>
       <c r="R16" t="n">
-        <v>6773405</v>
+        <v>6773937</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291351</v>
+        <v>128291026</v>
       </c>
       <c r="B17" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496519</v>
+        <v>496584</v>
       </c>
       <c r="R17" t="n">
-        <v>6773715</v>
+        <v>6773405</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291330</v>
+        <v>128291351</v>
       </c>
       <c r="B18" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496633</v>
+        <v>496519</v>
       </c>
       <c r="R18" t="n">
-        <v>6773937</v>
+        <v>6773715</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2519,7 +2519,7 @@
         <v>128291021</v>
       </c>
       <c r="B19" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>128291331</v>
       </c>
       <c r="B20" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291324</v>
+        <v>128291352</v>
       </c>
       <c r="B21" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496609</v>
+        <v>496573</v>
       </c>
       <c r="R21" t="n">
-        <v>6773957</v>
+        <v>6774008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B22" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R22" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291353</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496606</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774292</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128291328</v>
+        <v>128291028</v>
       </c>
       <c r="B24" t="n">
-        <v>57686</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,21 +3062,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3086,10 +3086,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496524</v>
+        <v>496510</v>
       </c>
       <c r="R24" t="n">
-        <v>6773501</v>
+        <v>6773105</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3158,10 +3158,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128291028</v>
+        <v>128291328</v>
       </c>
       <c r="B25" t="n">
-        <v>79089</v>
+        <v>57713</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3169,21 +3169,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496510</v>
+        <v>496524</v>
       </c>
       <c r="R25" t="n">
-        <v>6773105</v>
+        <v>6773501</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,7 +3268,7 @@
         <v>128291018</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>128291322</v>
       </c>
       <c r="B28" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>128291013</v>
       </c>
       <c r="B29" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>128311720</v>
       </c>
       <c r="B31" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291029</v>
+        <v>128291333</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496621</v>
+        <v>496585</v>
       </c>
       <c r="R6" t="n">
-        <v>6773167</v>
+        <v>6774537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291349</v>
+        <v>128291029</v>
       </c>
       <c r="B7" t="n">
         <v>79116</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496580</v>
+        <v>496621</v>
       </c>
       <c r="R7" t="n">
-        <v>6774075</v>
+        <v>6773167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291333</v>
+        <v>128291349</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496585</v>
+        <v>496580</v>
       </c>
       <c r="R8" t="n">
-        <v>6774537</v>
+        <v>6774075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128291330</v>
+        <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>57713</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,21 +2206,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2230,10 +2230,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496633</v>
+        <v>496584</v>
       </c>
       <c r="R16" t="n">
-        <v>6773937</v>
+        <v>6773405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128291026</v>
+        <v>128291351</v>
       </c>
       <c r="B17" t="n">
         <v>79116</v>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496584</v>
+        <v>496519</v>
       </c>
       <c r="R17" t="n">
-        <v>6773405</v>
+        <v>6773715</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128291351</v>
+        <v>128291330</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2420,21 +2420,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,10 +2444,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496519</v>
+        <v>496633</v>
       </c>
       <c r="R18" t="n">
-        <v>6773715</v>
+        <v>6773937</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R20" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291333</v>
+        <v>128291349</v>
       </c>
       <c r="B6" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496585</v>
+        <v>496580</v>
       </c>
       <c r="R6" t="n">
-        <v>6774537</v>
+        <v>6774075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1235,7 @@
         <v>128291029</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291349</v>
+        <v>128291333</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496580</v>
+        <v>496585</v>
       </c>
       <c r="R8" t="n">
-        <v>6774075</v>
+        <v>6774537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R9" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R10" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,32 +1660,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128291339</v>
+        <v>128291016</v>
       </c>
       <c r="B11" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496650</v>
+        <v>496578</v>
       </c>
       <c r="R11" t="n">
-        <v>6774498</v>
+        <v>6773580</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1767,32 +1767,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128291016</v>
+        <v>128291339</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496578</v>
+        <v>496650</v>
       </c>
       <c r="R12" t="n">
-        <v>6773580</v>
+        <v>6774498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,7 +1877,7 @@
         <v>128291348</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R14" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R15" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2198,7 +2198,7 @@
         <v>128291026</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>128291351</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291324</v>
+        <v>128291331</v>
       </c>
       <c r="B20" t="n">
-        <v>57716</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,16 +2634,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496609</v>
+        <v>496594</v>
       </c>
       <c r="R20" t="n">
-        <v>6773957</v>
+        <v>6774151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291352</v>
+        <v>128291353</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496573</v>
+        <v>496606</v>
       </c>
       <c r="R21" t="n">
-        <v>6774008</v>
+        <v>6774292</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291353</v>
+        <v>128291352</v>
       </c>
       <c r="B22" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496606</v>
+        <v>496573</v>
       </c>
       <c r="R22" t="n">
-        <v>6774292</v>
+        <v>6774008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291331</v>
+        <v>128291324</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,16 +2955,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496594</v>
+        <v>496609</v>
       </c>
       <c r="R23" t="n">
-        <v>6774151</v>
+        <v>6773957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,7 +3054,7 @@
         <v>128291028</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128291025</v>
+        <v>128291322</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,34 +3383,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496582</v>
+        <v>496530</v>
       </c>
       <c r="R27" t="n">
-        <v>6773525</v>
+        <v>6774395</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3442,7 +3450,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3452,7 +3460,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3479,10 +3492,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128291322</v>
+        <v>128291025</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3490,42 +3503,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496530</v>
+        <v>496582</v>
       </c>
       <c r="R28" t="n">
-        <v>6774395</v>
+        <v>6773525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3557,7 +3562,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3567,12 +3572,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>högt upp i tall</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3722,7 +3722,7 @@
         <v>128291346</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,7 +1125,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291349</v>
+        <v>128291029</v>
       </c>
       <c r="B6" t="n">
         <v>79120</v>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496580</v>
+        <v>496621</v>
       </c>
       <c r="R6" t="n">
-        <v>6774075</v>
+        <v>6773167</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291029</v>
+        <v>128291349</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496621</v>
+        <v>496580</v>
       </c>
       <c r="R7" t="n">
-        <v>6773167</v>
+        <v>6774075</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B9" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R9" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R10" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1981,7 +1981,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128291343</v>
+        <v>128291347</v>
       </c>
       <c r="B14" t="n">
         <v>79120</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496511</v>
+        <v>496603</v>
       </c>
       <c r="R14" t="n">
-        <v>6773404</v>
+        <v>6773923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128291347</v>
+        <v>128291343</v>
       </c>
       <c r="B15" t="n">
         <v>79120</v>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496603</v>
+        <v>496511</v>
       </c>
       <c r="R15" t="n">
-        <v>6773923</v>
+        <v>6773404</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291331</v>
+        <v>128291352</v>
       </c>
       <c r="B20" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496594</v>
+        <v>496573</v>
       </c>
       <c r="R20" t="n">
-        <v>6774151</v>
+        <v>6774008</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291352</v>
+        <v>128291331</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496573</v>
+        <v>496594</v>
       </c>
       <c r="R22" t="n">
-        <v>6774008</v>
+        <v>6774151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3372,10 +3372,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128291322</v>
+        <v>128291025</v>
       </c>
       <c r="B27" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3383,42 +3383,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496530</v>
+        <v>496582</v>
       </c>
       <c r="R27" t="n">
-        <v>6774395</v>
+        <v>6773525</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3450,7 +3442,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3460,12 +3452,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>högt upp i tall</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3492,10 +3479,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128291025</v>
+        <v>128291322</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,34 +3490,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kallåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496582</v>
+        <v>496530</v>
       </c>
       <c r="R28" t="n">
-        <v>6773525</v>
+        <v>6774395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3557,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3572,7 +3567,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:42</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>högt upp i tall</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 22701-2025 artfynd.xlsx
+++ b/artfynd/A 22701-2025 artfynd.xlsx
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128291029</v>
+        <v>128291333</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496621</v>
+        <v>496585</v>
       </c>
       <c r="R6" t="n">
-        <v>6773167</v>
+        <v>6774537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:33</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,7 +1232,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128291349</v>
+        <v>128291029</v>
       </c>
       <c r="B7" t="n">
         <v>79120</v>
@@ -1267,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496580</v>
+        <v>496621</v>
       </c>
       <c r="R7" t="n">
-        <v>6774075</v>
+        <v>6773167</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1339,10 +1339,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128291333</v>
+        <v>128291349</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496585</v>
+        <v>496580</v>
       </c>
       <c r="R8" t="n">
-        <v>6774537</v>
+        <v>6774075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1446,32 +1446,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128291020</v>
+        <v>128291338</v>
       </c>
       <c r="B9" t="n">
-        <v>57713</v>
+        <v>8450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496610</v>
+        <v>496516</v>
       </c>
       <c r="R9" t="n">
-        <v>6773043</v>
+        <v>6773458</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128291338</v>
+        <v>128291020</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496516</v>
+        <v>496610</v>
       </c>
       <c r="R10" t="n">
-        <v>6773458</v>
+        <v>6773043</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128291352</v>
+        <v>128291331</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496573</v>
+        <v>496594</v>
       </c>
       <c r="R20" t="n">
-        <v>6774008</v>
+        <v>6774151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2730,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128291353</v>
+        <v>128291324</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,21 +2741,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496606</v>
+        <v>496609</v>
       </c>
       <c r="R21" t="n">
-        <v>6774292</v>
+        <v>6773957</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128291331</v>
+        <v>128291352</v>
       </c>
       <c r="B22" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2848,21 +2848,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496594</v>
+        <v>496573</v>
       </c>
       <c r="R22" t="n">
-        <v>6774151</v>
+        <v>6774008</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128291324</v>
+        <v>128291353</v>
       </c>
       <c r="B23" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,21 +2955,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496609</v>
+        <v>496606</v>
       </c>
       <c r="R23" t="n">
-        <v>6773957</v>
+        <v>6774292</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
